--- a/e_commerce_forms/003_final_payment_form--e_commerce_forms.xlsx
+++ b/e_commerce_forms/003_final_payment_form--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1075,12 +1075,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option25</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option25</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option26</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option26</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option27</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option27</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option28</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option28</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option29</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option29</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option30</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option30</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option31</t>
+          <t>option_31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option31</t>
+          <t>Option 31</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option32</t>
+          <t>option_32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option32</t>
+          <t>Option 32</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option33</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option33</t>
+          <t>Option 33</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option33</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option33</t>
+          <t>Option 34</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option34</t>
+          <t>option_35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option34</t>
+          <t>Option 35</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option35</t>
+          <t>option_36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option35</t>
+          <t>Option 36</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option36</t>
+          <t>option_37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option36</t>
+          <t>Option 37</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option37</t>
+          <t>option_38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option37</t>
+          <t>Option 38</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option38</t>
+          <t>option_39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option38</t>
+          <t>Option 39</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option39</t>
+          <t>option_40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option39</t>
+          <t>Option 40</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option40</t>
+          <t>option_41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option40</t>
+          <t>Option 41</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option41</t>
+          <t>option_42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option41</t>
+          <t>Option 42</t>
         </is>
       </c>
     </row>
@@ -1924,12 +1924,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option42</t>
+          <t>option_43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option42</t>
+          <t>Option 43</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option43</t>
+          <t>option_44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option43</t>
+          <t>Option 44</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option44</t>
+          <t>option_45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option44</t>
+          <t>Option 45</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option45</t>
+          <t>option_46</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option45</t>
+          <t>Option 46</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option46</t>
+          <t>option_47</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option46</t>
+          <t>Option 47</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option47</t>
+          <t>option_48</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option47</t>
+          <t>Option 48</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option48</t>
+          <t>option_49</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option48</t>
+          <t>Option 49</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option49</t>
+          <t>option_50</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>option49</t>
+          <t>Option 50</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option50</t>
+          <t>option_51</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>option50</t>
+          <t>Option 51</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>option51</t>
+          <t>option_52</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>option51</t>
+          <t>Option 52</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>option52</t>
+          <t>option_53</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>option52</t>
+          <t>Option 53</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>option53</t>
+          <t>option_54</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>option53</t>
+          <t>Option 54</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>option54</t>
+          <t>option_55</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>option54</t>
+          <t>Option 55</t>
         </is>
       </c>
     </row>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>option55</t>
+          <t>option_56</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>option55</t>
+          <t>Option 56</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>option56</t>
+          <t>option_57</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>option56</t>
+          <t>Option 57</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>option57</t>
+          <t>option_58</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>option57</t>
+          <t>Option 58</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>option58</t>
+          <t>option_59</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>option58</t>
+          <t>Option 59</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>option59</t>
+          <t>option_60</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>option59</t>
+          <t>Option 60</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>option60</t>
+          <t>option_61</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>option60</t>
+          <t>Option 61</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>option61</t>
+          <t>option_62</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>option61</t>
+          <t>Option 62</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>option62</t>
+          <t>option_63</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>option62</t>
+          <t>Option 63</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2281,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>option63</t>
+          <t>option_64</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>option63</t>
+          <t>Option 64</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>option64</t>
+          <t>option_65</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>option64</t>
+          <t>Option 65</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2315,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>option65</t>
+          <t>option_66</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>option65</t>
+          <t>Option 66</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>option66</t>
+          <t>option_67</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>option66</t>
+          <t>Option 67</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>option67</t>
+          <t>option_68</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>option67</t>
+          <t>Option 68</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>option68</t>
+          <t>option_69</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>option68</t>
+          <t>Option 69</t>
         </is>
       </c>
     </row>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>option69</t>
+          <t>option_70</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>option69</t>
+          <t>Option 70</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>option70</t>
+          <t>option_71</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>option70</t>
+          <t>Option 71</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>option71</t>
+          <t>option_72</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>option71</t>
+          <t>Option 72</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>option72</t>
+          <t>option_73</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>option72</t>
+          <t>Option 73</t>
         </is>
       </c>
     </row>
@@ -2451,12 +2451,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>option73</t>
+          <t>option_74</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>option73</t>
+          <t>Option 74</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>option74</t>
+          <t>option_75</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>option74</t>
+          <t>Option 75</t>
         </is>
       </c>
     </row>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>option75</t>
+          <t>option_76</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>option75</t>
+          <t>Option 76</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>option76</t>
+          <t>option_77</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>option76</t>
+          <t>Option 77</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>option77</t>
+          <t>option_78</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>option77</t>
+          <t>Option 78</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>option78</t>
+          <t>option_79</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>option78</t>
+          <t>Option 79</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>option79</t>
+          <t>option_80</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>option79</t>
+          <t>Option 80</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>option80</t>
+          <t>option_81</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>option80</t>
+          <t>Option 81</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>option81</t>
+          <t>option_82</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>option81</t>
+          <t>Option 82</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>option82</t>
+          <t>option_83</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>option82</t>
+          <t>Option 83</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>option83</t>
+          <t>option_84</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>option83</t>
+          <t>Option 84</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>option84</t>
+          <t>option_85</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>option84</t>
+          <t>Option 85</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>option85</t>
+          <t>option_86</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>option85</t>
+          <t>Option 86</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>option86</t>
+          <t>option_87</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>option86</t>
+          <t>Option 87</t>
         </is>
       </c>
     </row>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>option87</t>
+          <t>option_88</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>option87</t>
+          <t>Option 88</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>option88</t>
+          <t>option_89</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>option88</t>
+          <t>Option 89</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>option89</t>
+          <t>option_90</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>option89</t>
+          <t>Option 90</t>
         </is>
       </c>
     </row>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>option90</t>
+          <t>option_91</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>option90</t>
+          <t>Option 91</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>option91</t>
+          <t>option_92</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>option91</t>
+          <t>Option 92</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>option92</t>
+          <t>option_93</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>option92</t>
+          <t>Option 93</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>option93</t>
+          <t>option_94</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>option93</t>
+          <t>Option 94</t>
         </is>
       </c>
     </row>
@@ -2808,12 +2808,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>option94</t>
+          <t>option_95</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>option94</t>
+          <t>Option 95</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>option95</t>
+          <t>option_96</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>option95</t>
+          <t>Option 96</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>option96</t>
+          <t>option_97</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>option96</t>
+          <t>Option 97</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>option97</t>
+          <t>option_98</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>option97</t>
+          <t>Option 98</t>
         </is>
       </c>
     </row>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>option98</t>
+          <t>option_99</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>option98</t>
+          <t>Option 99</t>
         </is>
       </c>
     </row>
@@ -2893,29 +2893,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>option99</t>
+          <t>option_100</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>option99</t>
+          <t>Option 100</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>confirm_payment_choices</t>
+          <t>confirm_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>option100</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>option100</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2944,29 +2944,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>confirm_choices</t>
+          <t>confirm_phone_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2995,29 +2995,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>confirm_phone_choices</t>
+          <t>confirm_email_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3046,29 +3046,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>confirm_email_choices</t>
+          <t>payment_method2_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3097,29 +3097,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>payment_method2_choices</t>
+          <t>confirm_payment_method2_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3148,29 +3148,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>confirm_payment_method2_choices</t>
+          <t>payment_method3_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3199,29 +3199,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>payment_method3_choices</t>
+          <t>confirm_payment_method3_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3250,29 +3250,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>confirm_payment_method3_choices</t>
+          <t>confirm_time_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3301,29 +3301,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>confirm_time_choices</t>
+          <t>confirm_address_choices</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3352,29 +3352,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>confirm_address_choices</t>
+          <t>confirm_payment_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3403,29 +3403,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>confirm_payment_choices</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
